--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_VÍTALY LA MAR BCBADAJOZ.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_VÍTALY LA MAR BCBADAJOZ.xlsx
@@ -565,13 +565,13 @@
         <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>84.76690000000001</v>
+        <v>100.5066</v>
       </c>
       <c r="E2" t="n">
-        <v>66.2002</v>
+        <v>76.2118</v>
       </c>
       <c r="F2" t="n">
-        <v>18.5671</v>
+        <v>24.2951</v>
       </c>
       <c r="G2" t="n">
         <v>60.61749999999999</v>
@@ -610,13 +610,13 @@
         <v>54.6598</v>
       </c>
       <c r="S2" t="n">
-        <v>-13.7537</v>
+        <v>1.9859</v>
       </c>
       <c r="T2" t="n">
-        <v>-13.3192</v>
+        <v>-3.3073</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4345999999999998</v>
+        <v>5.2932</v>
       </c>
       <c r="V2" t="n">
         <v>21.9687</v>
@@ -643,13 +643,13 @@
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>79.93559999999999</v>
+        <v>93.95829999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>60.9639</v>
+        <v>70.59529999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>18.9718</v>
+        <v>23.3626</v>
       </c>
       <c r="G3" t="n">
         <v>67.2362</v>
@@ -688,13 +688,13 @@
         <v>51.3243</v>
       </c>
       <c r="S3" t="n">
-        <v>-11.463</v>
+        <v>2.5597</v>
       </c>
       <c r="T3" t="n">
-        <v>-11.1005</v>
+        <v>-1.4688</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3622999999999999</v>
+        <v>4.0285</v>
       </c>
       <c r="V3" t="n">
         <v>7.1159</v>
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>50.0151</v>
+        <v>40.1876</v>
       </c>
       <c r="E4" t="n">
-        <v>28.844</v>
+        <v>23.3714</v>
       </c>
       <c r="F4" t="n">
-        <v>21.1713</v>
+        <v>16.8166</v>
       </c>
       <c r="G4" t="n">
         <v>27.3194</v>
@@ -766,13 +766,13 @@
         <v>44.8394</v>
       </c>
       <c r="S4" t="n">
-        <v>20.6826</v>
+        <v>10.8551</v>
       </c>
       <c r="T4" t="n">
-        <v>9.186400000000001</v>
+        <v>3.7138</v>
       </c>
       <c r="U4" t="n">
-        <v>11.4962</v>
+        <v>7.141</v>
       </c>
       <c r="V4" t="n">
         <v>1.6429</v>
@@ -799,13 +799,13 @@
         <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>49.554</v>
+        <v>38.4449</v>
       </c>
       <c r="E5" t="n">
-        <v>28.5543</v>
+        <v>21.0252</v>
       </c>
       <c r="F5" t="n">
-        <v>20.9998</v>
+        <v>17.4198</v>
       </c>
       <c r="G5" t="n">
         <v>8.857900000000001</v>
@@ -844,13 +844,13 @@
         <v>24.2725</v>
       </c>
       <c r="S5" t="n">
-        <v>20.2519</v>
+        <v>9.1431</v>
       </c>
       <c r="T5" t="n">
-        <v>10.3155</v>
+        <v>2.7864</v>
       </c>
       <c r="U5" t="n">
-        <v>9.9366</v>
+        <v>6.3566</v>
       </c>
       <c r="V5" t="n">
         <v>13.218</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>I. VAZQUEZ FLORES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>34.1764</v>
+        <v>35.686</v>
       </c>
       <c r="E6" t="n">
-        <v>26.9953</v>
+        <v>26.6469</v>
       </c>
       <c r="F6" t="n">
-        <v>7.181</v>
+        <v>9.039100000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0329000000000006</v>
+        <v>7.9023</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8266</v>
+        <v>1.6799</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7934</v>
+        <v>6.222499999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>17.3153</v>
+        <v>26.7895</v>
       </c>
       <c r="K6" t="n">
-        <v>11.5928</v>
+        <v>16.2767</v>
       </c>
       <c r="L6" t="n">
-        <v>5.723</v>
+        <v>10.5128</v>
       </c>
       <c r="M6" t="n">
-        <v>-17.3486</v>
+        <v>-18.8871</v>
       </c>
       <c r="N6" t="n">
-        <v>-13.4186</v>
+        <v>-14.5968</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.9294</v>
+        <v>-4.2902</v>
       </c>
       <c r="P6" t="n">
-        <v>9.8202</v>
+        <v>4.632099999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-25.9399</v>
+        <v>-32.7958</v>
       </c>
       <c r="R6" t="n">
-        <v>35.7602</v>
+        <v>37.4281</v>
       </c>
       <c r="S6" t="n">
-        <v>17.1505</v>
+        <v>1.7487</v>
       </c>
       <c r="T6" t="n">
-        <v>16.7445</v>
+        <v>-0.3897</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4056999999999999</v>
+        <v>2.1386</v>
       </c>
       <c r="V6" t="n">
-        <v>7.2385</v>
+        <v>21.4027</v>
       </c>
       <c r="W6" t="n">
-        <v>18.875</v>
+        <v>33.0431</v>
       </c>
       <c r="X6" t="n">
-        <v>-11.6366</v>
+        <v>-11.6405</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>29.2303</v>
+        <v>29.9861</v>
       </c>
       <c r="E8" t="n">
-        <v>14.8465</v>
+        <v>0.6662000000000012</v>
       </c>
       <c r="F8" t="n">
-        <v>14.3841</v>
+        <v>29.32</v>
       </c>
       <c r="G8" t="n">
-        <v>20.6724</v>
+        <v>-0.5472999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>11.7062</v>
+        <v>-2.4076</v>
       </c>
       <c r="I8" t="n">
-        <v>8.9666</v>
+        <v>1.8604</v>
       </c>
       <c r="J8" t="n">
-        <v>48.1694</v>
+        <v>12.812</v>
       </c>
       <c r="K8" t="n">
-        <v>31.1046</v>
+        <v>8.4664</v>
       </c>
       <c r="L8" t="n">
-        <v>17.0647</v>
+        <v>4.3455</v>
       </c>
       <c r="M8" t="n">
-        <v>-27.4965</v>
+        <v>-13.3592</v>
       </c>
       <c r="N8" t="n">
-        <v>-19.3986</v>
+        <v>-10.874</v>
       </c>
       <c r="O8" t="n">
-        <v>-8.0983</v>
+        <v>-2.4853</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6677</v>
+        <v>5.5587</v>
       </c>
       <c r="Q8" t="n">
-        <v>-58.5505</v>
+        <v>-34.6486</v>
       </c>
       <c r="R8" t="n">
-        <v>56.8832</v>
+        <v>40.2074</v>
       </c>
       <c r="S8" t="n">
-        <v>13.4379</v>
+        <v>1.6904</v>
       </c>
       <c r="T8" t="n">
-        <v>7.611</v>
+        <v>-1.4082</v>
       </c>
       <c r="U8" t="n">
-        <v>5.827199999999999</v>
+        <v>3.0985</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.2127</v>
+        <v>23.2847</v>
       </c>
       <c r="W8" t="n">
-        <v>17.6168</v>
+        <v>23.9114</v>
       </c>
       <c r="X8" t="n">
-        <v>-20.8296</v>
+        <v>-0.6262</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>26.6781</v>
+        <v>26.0181</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5503</v>
+        <v>10.8109</v>
       </c>
       <c r="F9" t="n">
-        <v>23.1279</v>
+        <v>15.2068</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3273</v>
+        <v>20.6724</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2105</v>
+        <v>11.7062</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1168</v>
+        <v>8.9666</v>
       </c>
       <c r="J9" t="n">
-        <v>11.13</v>
+        <v>48.1694</v>
       </c>
       <c r="K9" t="n">
-        <v>10.0681</v>
+        <v>31.1046</v>
       </c>
       <c r="L9" t="n">
-        <v>1.062</v>
+        <v>17.0647</v>
       </c>
       <c r="M9" t="n">
-        <v>-14.4576</v>
+        <v>-27.4965</v>
       </c>
       <c r="N9" t="n">
-        <v>-12.2786</v>
+        <v>-19.3986</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1788</v>
+        <v>-8.0983</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6677</v>
+        <v>-1.6677</v>
       </c>
       <c r="Q9" t="n">
-        <v>-32.7958</v>
+        <v>-58.5505</v>
       </c>
       <c r="R9" t="n">
-        <v>34.4633</v>
+        <v>56.8832</v>
       </c>
       <c r="S9" t="n">
-        <v>25.0056</v>
+        <v>10.2257</v>
       </c>
       <c r="T9" t="n">
-        <v>13.2653</v>
+        <v>3.5756</v>
       </c>
       <c r="U9" t="n">
-        <v>11.7406</v>
+        <v>6.649900000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>3.3323</v>
+        <v>-3.2127</v>
       </c>
       <c r="W9" t="n">
-        <v>11.9509</v>
+        <v>17.6168</v>
       </c>
       <c r="X9" t="n">
-        <v>-8.618500000000001</v>
+        <v>-20.8296</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ FLORES</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>25.7204</v>
+        <v>24.8293</v>
       </c>
       <c r="E10" t="n">
-        <v>19.9762</v>
+        <v>15.9522</v>
       </c>
       <c r="F10" t="n">
-        <v>5.744199999999999</v>
+        <v>8.877800000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>7.9023</v>
+        <v>-0.0329000000000006</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6799</v>
+        <v>-1.8266</v>
       </c>
       <c r="I10" t="n">
-        <v>6.222499999999999</v>
+        <v>1.7934</v>
       </c>
       <c r="J10" t="n">
-        <v>26.7895</v>
+        <v>17.3153</v>
       </c>
       <c r="K10" t="n">
-        <v>16.2767</v>
+        <v>11.5928</v>
       </c>
       <c r="L10" t="n">
-        <v>10.5128</v>
+        <v>5.723</v>
       </c>
       <c r="M10" t="n">
-        <v>-18.8871</v>
+        <v>-17.3486</v>
       </c>
       <c r="N10" t="n">
-        <v>-14.5968</v>
+        <v>-13.4186</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.2902</v>
+        <v>-3.9294</v>
       </c>
       <c r="P10" t="n">
-        <v>4.632099999999999</v>
+        <v>9.8202</v>
       </c>
       <c r="Q10" t="n">
-        <v>-32.7958</v>
+        <v>-25.9399</v>
       </c>
       <c r="R10" t="n">
-        <v>37.4281</v>
+        <v>35.7602</v>
       </c>
       <c r="S10" t="n">
-        <v>-8.216699999999999</v>
+        <v>7.8039</v>
       </c>
       <c r="T10" t="n">
-        <v>-7.0604</v>
+        <v>5.7017</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1564</v>
+        <v>2.1025</v>
       </c>
       <c r="V10" t="n">
-        <v>21.4027</v>
+        <v>7.2385</v>
       </c>
       <c r="W10" t="n">
-        <v>33.0431</v>
+        <v>18.875</v>
       </c>
       <c r="X10" t="n">
-        <v>-11.6405</v>
+        <v>-11.6366</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>J. PAREDES BERMEJO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>22.1457</v>
+        <v>17.3677</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.396100000000001</v>
+        <v>13.2215</v>
       </c>
       <c r="F11" t="n">
-        <v>28.5418</v>
+        <v>4.146299999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5472999999999999</v>
+        <v>11.0834</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.4076</v>
+        <v>4.557599999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8604</v>
+        <v>6.526000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>12.812</v>
+        <v>22.5932</v>
       </c>
       <c r="K11" t="n">
-        <v>8.4664</v>
+        <v>14.4569</v>
       </c>
       <c r="L11" t="n">
-        <v>4.3455</v>
+        <v>8.1364</v>
       </c>
       <c r="M11" t="n">
-        <v>-13.3592</v>
+        <v>-11.5099</v>
       </c>
       <c r="N11" t="n">
-        <v>-10.874</v>
+        <v>-9.8994</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.4853</v>
+        <v>-1.6105</v>
       </c>
       <c r="P11" t="n">
-        <v>5.5587</v>
+        <v>17.9728</v>
       </c>
       <c r="Q11" t="n">
-        <v>-34.6486</v>
+        <v>-10.0054</v>
       </c>
       <c r="R11" t="n">
-        <v>40.2074</v>
+        <v>27.9781</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.1503</v>
+        <v>1.3376</v>
       </c>
       <c r="T11" t="n">
-        <v>-8.470499999999999</v>
+        <v>-0.3096000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>2.3204</v>
+        <v>1.6475</v>
       </c>
       <c r="V11" t="n">
-        <v>23.2847</v>
+        <v>-13.0263</v>
       </c>
       <c r="W11" t="n">
-        <v>23.9114</v>
+        <v>0.9432</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6262</v>
+        <v>-13.9696</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. PAREDES BERMEJO</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>14.385</v>
+        <v>13.9147</v>
       </c>
       <c r="E12" t="n">
-        <v>11.8936</v>
+        <v>-5.7616</v>
       </c>
       <c r="F12" t="n">
-        <v>2.491400000000001</v>
+        <v>19.6764</v>
       </c>
       <c r="G12" t="n">
-        <v>11.0834</v>
+        <v>-3.3273</v>
       </c>
       <c r="H12" t="n">
-        <v>4.557599999999999</v>
+        <v>-2.2105</v>
       </c>
       <c r="I12" t="n">
-        <v>6.526000000000001</v>
+        <v>-1.1168</v>
       </c>
       <c r="J12" t="n">
-        <v>22.5932</v>
+        <v>11.13</v>
       </c>
       <c r="K12" t="n">
-        <v>14.4569</v>
+        <v>10.0681</v>
       </c>
       <c r="L12" t="n">
-        <v>8.1364</v>
+        <v>1.062</v>
       </c>
       <c r="M12" t="n">
-        <v>-11.5099</v>
+        <v>-14.4576</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.8994</v>
+        <v>-12.2786</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6105</v>
+        <v>-2.1788</v>
       </c>
       <c r="P12" t="n">
-        <v>17.9728</v>
+        <v>1.6677</v>
       </c>
       <c r="Q12" t="n">
-        <v>-10.0054</v>
+        <v>-32.7958</v>
       </c>
       <c r="R12" t="n">
-        <v>27.9781</v>
+        <v>34.4633</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6448</v>
+        <v>12.2422</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6375</v>
+        <v>3.9531</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.007400000000000129</v>
+        <v>8.2889</v>
       </c>
       <c r="V12" t="n">
-        <v>-13.0263</v>
+        <v>3.3323</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9432</v>
+        <v>11.9509</v>
       </c>
       <c r="X12" t="n">
-        <v>-13.9696</v>
+        <v>-8.618500000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. RODRÍGUEZ LEIRO</t>
+          <t>A. CUADRA CRESPO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6988</v>
+        <v>6.1458</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6988</v>
+        <v>-0.6343999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>6.7801</v>
       </c>
       <c r="G13" t="n">
-        <v>4.6988</v>
+        <v>0.8394</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9661999999999999</v>
+        <v>1.0536</v>
       </c>
       <c r="I13" t="n">
-        <v>3.7326</v>
+        <v>-0.2136999999999998</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6988</v>
+        <v>5.4779</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9661999999999999</v>
+        <v>6.0844</v>
       </c>
       <c r="L13" t="n">
-        <v>3.7326</v>
+        <v>-0.6064000000000002</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-4.6386</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-5.031</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.3927</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.2235</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-8.708400000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>10.932</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0.06439999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-0.8651</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.8007</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>3.1472</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.461</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.3138</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTÍN</t>
+          <t>A. RODRÍGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,34 +1498,34 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>4.443</v>
+        <v>4.6988</v>
       </c>
       <c r="E14" t="n">
-        <v>4.443</v>
+        <v>4.6988</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>4.443</v>
+        <v>4.6988</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5768</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8663</v>
+        <v>3.7326</v>
       </c>
       <c r="J14" t="n">
-        <v>4.443</v>
+        <v>4.6988</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5768</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8663</v>
+        <v>3.7326</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. CUADRA CRESPO</t>
+          <t>J. NIELSEN HIDALGO MARTÍN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1368</v>
+        <v>4.443</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.725</v>
+        <v>4.443</v>
       </c>
       <c r="F15" t="n">
-        <v>5.8619</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8394</v>
+        <v>4.443</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0536</v>
+        <v>2.5768</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2136999999999998</v>
+        <v>1.8663</v>
       </c>
       <c r="J15" t="n">
-        <v>5.4779</v>
+        <v>4.443</v>
       </c>
       <c r="K15" t="n">
-        <v>6.0844</v>
+        <v>2.5768</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6064000000000002</v>
+        <v>1.8663</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.6386</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-5.031</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3927</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2235</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-8.708400000000001</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>10.932</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.0733</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.9556</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1178000000000001</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>3.1472</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.461</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. YOUNG MEDIERO</t>
+          <t>L. MONES RIERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8249</v>
+        <v>0.06820000000000004</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.7298</v>
+        <v>-2.3025</v>
       </c>
       <c r="F16" t="n">
-        <v>6.5547</v>
+        <v>2.3707</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3752</v>
+        <v>-3.1764</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2639</v>
+        <v>-1.9307</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.6392</v>
+        <v>-1.2459</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1001</v>
+        <v>-2.545</v>
       </c>
       <c r="K16" t="n">
-        <v>6.0239</v>
+        <v>-0.3697</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.924300000000001</v>
+        <v>-2.1754</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.4752</v>
+        <v>-0.6313999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.7603</v>
+        <v>-1.5609</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2849</v>
+        <v>0.9296</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2234</v>
+        <v>1.8528</v>
       </c>
       <c r="Q16" t="n">
-        <v>-9.4495</v>
+        <v>-1.8529</v>
       </c>
       <c r="R16" t="n">
-        <v>11.6733</v>
+        <v>3.7057</v>
       </c>
       <c r="S16" t="n">
-        <v>3.7452</v>
+        <v>-0.1831</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7326999999999998</v>
+        <v>-0.1072</v>
       </c>
       <c r="U16" t="n">
-        <v>3.0129</v>
+        <v>-0.07590000000000002</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.7683</v>
+        <v>1.5749</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8873</v>
+        <v>2.2027</v>
       </c>
       <c r="X16" t="n">
-        <v>-4.6556</v>
+        <v>-0.6278</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. TOMPEA</t>
+          <t>A. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3574000000000002</v>
+        <v>-0.006500000000000505</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0146</v>
+        <v>-5.0671</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.372</v>
+        <v>5.0604</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0695</v>
+        <v>-1.3752</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1032999999999999</v>
+        <v>2.2639</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9661999999999999</v>
+        <v>-3.6392</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4598</v>
+        <v>2.1001</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4645</v>
+        <v>6.0239</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.0047</v>
+        <v>-3.924300000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5293</v>
+        <v>-3.4752</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.5678</v>
+        <v>-3.7603</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0385</v>
+        <v>0.2849</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7411</v>
+        <v>2.2234</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.7793</v>
+        <v>-9.4495</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0381</v>
+        <v>11.6733</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3965</v>
+        <v>1.9136</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3342</v>
+        <v>0.3956000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0624</v>
+        <v>1.5183</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9433</v>
+        <v>-2.7683</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.8873</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9433</v>
+        <v>-4.6556</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. MONES RIERA</t>
+          <t>L. TOMPEA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8869000000000002</v>
+        <v>-1.5008</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.1838</v>
+        <v>-0.3995999999999995</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2968</v>
+        <v>-1.1011</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.1764</v>
+        <v>-1.0695</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9307</v>
+        <v>-0.1032999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2459</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.545</v>
+        <v>1.4598</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3697</v>
+        <v>2.4645</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.1754</v>
+        <v>-1.0047</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6313999999999999</v>
+        <v>-2.5293</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5609</v>
+        <v>-2.5678</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9296</v>
+        <v>0.0385</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8528</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R18" t="n">
-        <v>3.7057</v>
+        <v>2.0381</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1383</v>
+        <v>1.2532</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9884999999999999</v>
+        <v>0.9198999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1498</v>
+        <v>0.3332</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5749</v>
+        <v>-0.9433</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2027</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6278</v>
+        <v>-0.9433</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. PIETRAS</t>
+          <t>J. RODRIGUEZ CAPELLIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6128</v>
+        <v>-1.6174</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7337</v>
+        <v>-3.6154</v>
       </c>
       <c r="F19" t="n">
-        <v>0.121</v>
+        <v>1.998</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.748</v>
+        <v>1.2618</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4009</v>
+        <v>1.6598</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6529</v>
+        <v>-0.3977999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5884</v>
+        <v>-0.3753000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5884</v>
+        <v>0.2147</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.5900000000000002</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1596</v>
+        <v>1.6371</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8124</v>
+        <v>1.4451</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6529</v>
+        <v>0.1922</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3089</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2189</v>
+        <v>-0.4606</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.09</v>
+        <v>-0.06590000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CAPELLIN</t>
+          <t>B. PIETRAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,70 +1966,70 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1579</v>
+        <v>-1.6872</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.8112</v>
+        <v>-1.6358</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6533</v>
+        <v>-0.0514</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2618</v>
+        <v>-0.748</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6598</v>
+        <v>-1.4009</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3977999999999999</v>
+        <v>0.6529</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3753000000000001</v>
+        <v>-0.5884</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2147</v>
+        <v>-0.5884</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5900000000000002</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6371</v>
+        <v>-0.1596</v>
       </c>
       <c r="N20" t="n">
-        <v>1.4451</v>
+        <v>-0.8124</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1922</v>
+        <v>0.6529</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0382</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7411</v>
+        <v>0.3706</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0672</v>
+        <v>-0.3833</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6565</v>
+        <v>-0.1209</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4106</v>
+        <v>-0.2624</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>25</v>
       </c>
       <c r="D21" t="n">
-        <v>-17.4512</v>
+        <v>-13.5477</v>
       </c>
       <c r="E21" t="n">
-        <v>-24.3969</v>
+        <v>-22.0349</v>
       </c>
       <c r="F21" t="n">
-        <v>6.945499999999999</v>
+        <v>8.4871</v>
       </c>
       <c r="G21" t="n">
         <v>-21.5356</v>
@@ -2092,13 +2092,13 @@
         <v>25.0139</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9207</v>
+        <v>1.9825</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.8038</v>
+        <v>-0.4421999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8832000000000001</v>
+        <v>2.4246</v>
       </c>
       <c r="V21" t="n">
         <v>-2.3326</v>
@@ -2125,13 +2125,13 @@
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>438.4897</v>
+        <v>449.1403999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>255.2491</v>
+        <v>257.4367999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>183.2416</v>
+        <v>191.7043</v>
       </c>
       <c r="G22" t="n">
         <v>214.3648</v>
@@ -2161,7 +2161,7 @@
         <v>-47.7877</v>
       </c>
       <c r="P22" t="n">
-        <v>89.86410000000001</v>
+        <v>89.86409999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>-372.4254</v>
@@ -2170,16 +2170,16 @@
         <v>462.291</v>
       </c>
       <c r="S22" t="n">
-        <v>52.9333</v>
+        <v>63.58410000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>9.978200000000001</v>
+        <v>12.1665</v>
       </c>
       <c r="U22" t="n">
-        <v>42.9563</v>
+        <v>51.4178</v>
       </c>
       <c r="V22" t="n">
-        <v>81.32819999999998</v>
+        <v>81.3282</v>
       </c>
       <c r="W22" t="n">
         <v>203.2538</v>
